--- a/ig/TEST-SUPPLEMENT/ValueSet-JDV-J88-AnneeUniversitaire-RASS.xlsx
+++ b/ig/TEST-SUPPLEMENT/ValueSet-JDV-J88-AnneeUniversitaire-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20200424120000</t>
+    <t>20251016120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-04-24T12:00:00+01:00</t>
+    <t>2025-10-16T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -97,6 +97,18 @@
   </si>
   <si>
     <t>Concept</t>
+  </si>
+  <si>
+    <t>AU0809</t>
+  </si>
+  <si>
+    <t>2008-2009</t>
+  </si>
+  <si>
+    <t>AU0910</t>
+  </si>
+  <si>
+    <t>2009-2010</t>
   </si>
   <si>
     <t>AU1011</t>
@@ -481,7 +493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -653,15 +665,31 @@
         <v>66</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
